--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Egypt Egyptian Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Egypt Egyptian Premier League_20242025.xlsx
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ5" t="n">
         <v>0.92</v>
@@ -1819,10 +1819,10 @@
         <v>5</v>
       </c>
       <c r="BB6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD6" t="n">
         <v>1.96</v>
@@ -2037,10 +2037,10 @@
         <v>6</v>
       </c>
       <c r="BB7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD7" t="n">
         <v>1.12</v>
@@ -4620,7 +4620,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -6361,7 +6361,7 @@
         <v>1</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.55</v>
@@ -7890,7 +7890,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="AR34" t="n">
         <v>0.5600000000000001</v>
@@ -9631,7 +9631,7 @@
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ42" t="n">
         <v>1.57</v>
@@ -11408,13 +11408,13 @@
         <v>3</v>
       </c>
       <c r="BA50" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB50" t="n">
         <v>3</v>
       </c>
       <c r="BC50" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD50" t="n">
         <v>1.16</v>
@@ -12937,10 +12937,10 @@
         <v>3</v>
       </c>
       <c r="BB57" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD57" t="n">
         <v>3.66</v>
@@ -13900,10 +13900,10 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -13912,7 +13912,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['-1', '-1', '-1']</t>
         </is>
       </c>
       <c r="Q62" t="n">
@@ -13991,10 +13991,10 @@
         <v>0</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ62" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="AR62" t="n">
         <v>1.21</v>
@@ -14009,19 +14009,19 @@
         <v>1</v>
       </c>
       <c r="AV62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW62" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX62" t="n">
         <v>4</v>
       </c>
       <c r="AY62" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ62" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA62" t="n">
         <v>4</v>
@@ -15078,22 +15078,22 @@
         <v>0.67</v>
       </c>
       <c r="AO67" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AP67" t="n">
         <v>1.45</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="AR67" t="n">
         <v>0.9</v>
       </c>
       <c r="AS67" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="AT67" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AU67" t="n">
         <v>3</v>
@@ -18345,25 +18345,25 @@
         <v>1.16</v>
       </c>
       <c r="AN82" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AO82" t="n">
         <v>2.33</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ82" t="n">
         <v>1.77</v>
       </c>
       <c r="AR82" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AS82" t="n">
         <v>1.36</v>
       </c>
       <c r="AT82" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AU82" t="n">
         <v>3</v>
@@ -18566,22 +18566,22 @@
         <v>1</v>
       </c>
       <c r="AO83" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="AP83" t="n">
         <v>1.09</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="AR83" t="n">
         <v>0.72</v>
       </c>
       <c r="AS83" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="AT83" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AU83" t="n">
         <v>3</v>
@@ -18605,10 +18605,10 @@
         <v>4</v>
       </c>
       <c r="BB83" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC83" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD83" t="n">
         <v>2.05</v>
@@ -21875,10 +21875,10 @@
         <v>5</v>
       </c>
       <c r="BB98" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC98" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD98" t="n">
         <v>1.98</v>
@@ -22269,25 +22269,25 @@
         <v>1.12</v>
       </c>
       <c r="AN100" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AO100" t="n">
         <v>1.8</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ100" t="n">
         <v>2.08</v>
       </c>
       <c r="AR100" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AS100" t="n">
         <v>1.36</v>
       </c>
       <c r="AT100" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AU100" t="n">
         <v>3</v>
@@ -22965,10 +22965,10 @@
         <v>2</v>
       </c>
       <c r="BB103" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC103" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD103" t="n">
         <v>1.21</v>
@@ -23798,22 +23798,22 @@
         <v>2.17</v>
       </c>
       <c r="AO107" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="AP107" t="n">
         <v>2</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="AR107" t="n">
         <v>1.6</v>
       </c>
       <c r="AS107" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="AT107" t="n">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="AU107" t="n">
         <v>4</v>
@@ -25106,22 +25106,22 @@
         <v>0.67</v>
       </c>
       <c r="AO113" t="n">
-        <v>0.17</v>
+        <v>0.5</v>
       </c>
       <c r="AP113" t="n">
         <v>1.17</v>
       </c>
       <c r="AQ113" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="AR113" t="n">
         <v>1.16</v>
       </c>
       <c r="AS113" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="AT113" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AU113" t="n">
         <v>4</v>
@@ -25975,25 +25975,25 @@
         <v>1.48</v>
       </c>
       <c r="AN117" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AO117" t="n">
         <v>2.4</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ117" t="n">
         <v>1.64</v>
       </c>
       <c r="AR117" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AS117" t="n">
         <v>1.08</v>
       </c>
       <c r="AT117" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AU117" t="n">
         <v>1</v>
@@ -27719,25 +27719,25 @@
         <v>1.16</v>
       </c>
       <c r="AN125" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AO125" t="n">
         <v>2</v>
       </c>
       <c r="AP125" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ125" t="n">
         <v>2.13</v>
       </c>
       <c r="AR125" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AS125" t="n">
         <v>1.27</v>
       </c>
       <c r="AT125" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="AU125" t="n">
         <v>0</v>
@@ -29248,22 +29248,22 @@
         <v>1.83</v>
       </c>
       <c r="AO132" t="n">
-        <v>0.14</v>
+        <v>0.43</v>
       </c>
       <c r="AP132" t="n">
         <v>1.83</v>
       </c>
       <c r="AQ132" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="AR132" t="n">
         <v>0.97</v>
       </c>
       <c r="AS132" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="AT132" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AU132" t="n">
         <v>0</v>
@@ -30335,25 +30335,25 @@
         <v>1.72</v>
       </c>
       <c r="AN137" t="n">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="AO137" t="n">
         <v>0.43</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ137" t="n">
         <v>1.23</v>
       </c>
       <c r="AR137" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AS137" t="n">
         <v>1</v>
       </c>
       <c r="AT137" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AU137" t="n">
         <v>5</v>
@@ -30810,13 +30810,13 @@
         <v>10</v>
       </c>
       <c r="BA139" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB139" t="n">
         <v>2</v>
       </c>
       <c r="BC139" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD139" t="n">
         <v>1.83</v>
@@ -32339,10 +32339,10 @@
         <v>6</v>
       </c>
       <c r="BB146" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC146" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD146" t="n">
         <v>1.41</v>
@@ -33172,22 +33172,22 @@
         <v>1.25</v>
       </c>
       <c r="AO150" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="AP150" t="n">
         <v>1.07</v>
       </c>
       <c r="AQ150" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="AR150" t="n">
         <v>1.03</v>
       </c>
       <c r="AS150" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="AT150" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AU150" t="n">
         <v>6</v>
@@ -34083,10 +34083,10 @@
         <v>5</v>
       </c>
       <c r="BB154" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC154" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD154" t="n">
         <v>1.62</v>
@@ -34259,25 +34259,25 @@
         <v>1.26</v>
       </c>
       <c r="AN155" t="n">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="AO155" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AP155" t="n">
-        <v>0.96</v>
+        <v>1.25</v>
       </c>
       <c r="AQ155" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AR155" t="n">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="AS155" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AT155" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="AU155" t="n">
         <v>3</v>
@@ -34286,16 +34286,16 @@
         <v>3</v>
       </c>
       <c r="AW155" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX155" t="n">
         <v>8</v>
       </c>
-      <c r="AX155" t="n">
-        <v>6</v>
-      </c>
       <c r="AY155" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ155" t="n">
         <v>11</v>
-      </c>
-      <c r="AZ155" t="n">
-        <v>9</v>
       </c>
       <c r="BA155" t="n">
         <v>5</v>
@@ -34367,7 +34367,7 @@
         <v>45727.6875</v>
       </c>
       <c r="F156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -34477,25 +34477,25 @@
         <v>1.19</v>
       </c>
       <c r="AN156" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AO156" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AP156" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ156" t="n">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="AR156" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="AS156" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="AT156" t="n">
-        <v>3.01</v>
+        <v>2.89</v>
       </c>
       <c r="AU156" t="n">
         <v>-1</v>
@@ -34695,37 +34695,37 @@
         <v>1.47</v>
       </c>
       <c r="AN157" t="n">
-        <v>0.59</v>
+        <v>0.67</v>
       </c>
       <c r="AO157" t="n">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="AP157" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ157" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AR157" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AS157" t="n">
         <v>1.08</v>
       </c>
-      <c r="AQ157" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR157" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="AS157" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AT157" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AU157" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV157" t="n">
         <v>5</v>
       </c>
-      <c r="AV157" t="n">
+      <c r="AW157" t="n">
         <v>6</v>
       </c>
-      <c r="AW157" t="n">
+      <c r="AX157" t="n">
         <v>7</v>
-      </c>
-      <c r="AX157" t="n">
-        <v>6</v>
       </c>
       <c r="AY157" t="n">
         <v>12</v>
@@ -34913,43 +34913,43 @@
         <v>1.38</v>
       </c>
       <c r="AN158" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AO158" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AP158" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AR158" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AS158" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AT158" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="AU158" t="n">
         <v>2</v>
       </c>
       <c r="AV158" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW158" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX158" t="n">
         <v>3</v>
       </c>
-      <c r="AW158" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX158" t="n">
-        <v>2</v>
-      </c>
       <c r="AY158" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ158" t="n">
         <v>8</v>
-      </c>
-      <c r="AZ158" t="n">
-        <v>5</v>
       </c>
       <c r="BA158" t="n">
         <v>11</v>
@@ -35131,34 +35131,34 @@
         <v>1.27</v>
       </c>
       <c r="AN159" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AO159" t="n">
-        <v>1.71</v>
+        <v>1.89</v>
       </c>
       <c r="AP159" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AQ159" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AR159" t="n">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="AS159" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AT159" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="AU159" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV159" t="n">
         <v>3</v>
       </c>
       <c r="AW159" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX159" t="n">
         <v>7</v>
@@ -35349,43 +35349,43 @@
         <v>2.06</v>
       </c>
       <c r="AN160" t="n">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="AO160" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AP160" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="AQ160" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AR160" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AS160" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="AT160" t="n">
-        <v>2.55</v>
+        <v>2.79</v>
       </c>
       <c r="AU160" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV160" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW160" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX160" t="n">
         <v>5</v>
       </c>
-      <c r="AW160" t="n">
+      <c r="AY160" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ160" t="n">
         <v>9</v>
-      </c>
-      <c r="AX160" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY160" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ160" t="n">
-        <v>8</v>
       </c>
       <c r="BA160" t="n">
         <v>3</v>
@@ -35567,40 +35567,40 @@
         <v>1.28</v>
       </c>
       <c r="AN161" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AO161" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AP161" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ161" t="n">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="AR161" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AS161" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AT161" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AU161" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV161" t="n">
         <v>4</v>
       </c>
       <c r="AW161" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AX161" t="n">
         <v>0</v>
       </c>
       <c r="AY161" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ161" t="n">
         <v>4</v>
@@ -35785,43 +35785,43 @@
         <v>1.58</v>
       </c>
       <c r="AN162" t="n">
-        <v>1.24</v>
+        <v>0.89</v>
       </c>
       <c r="AO162" t="n">
-        <v>0.71</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.16</v>
+        <v>0.79</v>
       </c>
       <c r="AQ162" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="AR162" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AS162" t="n">
         <v>0.87</v>
       </c>
       <c r="AT162" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="AU162" t="n">
         <v>3</v>
       </c>
       <c r="AV162" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AW162" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX162" t="n">
         <v>4</v>
       </c>
       <c r="AY162" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ162" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BA162" t="n">
         <v>5</v>
@@ -36003,43 +36003,43 @@
         <v>1.24</v>
       </c>
       <c r="AN163" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AO163" t="n">
-        <v>0.72</v>
+        <v>0.38</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AQ163" t="n">
-        <v>1.08</v>
+        <v>0.85</v>
       </c>
       <c r="AR163" t="n">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="AS163" t="n">
-        <v>0.99</v>
+        <v>0.93</v>
       </c>
       <c r="AT163" t="n">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="AU163" t="n">
         <v>3</v>
       </c>
       <c r="AV163" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW163" t="n">
         <v>1</v>
       </c>
       <c r="AX163" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AY163" t="n">
         <v>4</v>
       </c>
       <c r="AZ163" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BA163" t="n">
         <v>3</v>
@@ -36221,25 +36221,25 @@
         <v>1.36</v>
       </c>
       <c r="AN164" t="n">
-        <v>0.83</v>
+        <v>1.13</v>
       </c>
       <c r="AO164" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AP164" t="n">
-        <v>0.84</v>
+        <v>1</v>
       </c>
       <c r="AQ164" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AR164" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="AS164" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AT164" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AU164" t="n">
         <v>0</v>
@@ -36248,16 +36248,16 @@
         <v>1</v>
       </c>
       <c r="AW164" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX164" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY164" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ164" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BA164" t="n">
         <v>3</v>
@@ -36439,25 +36439,25 @@
         <v>1.85</v>
       </c>
       <c r="AN165" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AO165" t="n">
-        <v>1.11</v>
+        <v>0.78</v>
       </c>
       <c r="AP165" t="n">
-        <v>1.28</v>
+        <v>1.07</v>
       </c>
       <c r="AQ165" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AR165" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AS165" t="n">
-        <v>1.05</v>
+        <v>0.97</v>
       </c>
       <c r="AT165" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AU165" t="n">
         <v>6</v>
@@ -36466,13 +36466,13 @@
         <v>5</v>
       </c>
       <c r="AW165" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AX165" t="n">
         <v>2</v>
       </c>
       <c r="AY165" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AZ165" t="n">
         <v>7</v>
@@ -36657,43 +36657,43 @@
         <v>1.41</v>
       </c>
       <c r="AN166" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="AO166" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AP166" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ166" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR166" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AS166" t="n">
         <v>1.1</v>
       </c>
-      <c r="AS166" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AT166" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AU166" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV166" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW166" t="n">
         <v>3</v>
       </c>
-      <c r="AV166" t="n">
+      <c r="AX166" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY166" t="n">
         <v>4</v>
       </c>
-      <c r="AW166" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX166" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY166" t="n">
-        <v>5</v>
-      </c>
       <c r="AZ166" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA166" t="n">
         <v>3</v>
@@ -36875,40 +36875,40 @@
         <v>1.25</v>
       </c>
       <c r="AN167" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AO167" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AP167" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AQ167" t="n">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="AR167" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AS167" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AT167" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AU167" t="n">
         <v>2</v>
       </c>
       <c r="AV167" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW167" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AX167" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY167" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ167" t="n">
         <v>17</v>
@@ -37093,43 +37093,43 @@
         <v>1.29</v>
       </c>
       <c r="AN168" t="n">
-        <v>2.39</v>
+        <v>2.56</v>
       </c>
       <c r="AO168" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AP168" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="AQ168" t="n">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="AR168" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AS168" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="AT168" t="n">
-        <v>3.07</v>
+        <v>2.97</v>
       </c>
       <c r="AU168" t="n">
         <v>4</v>
       </c>
       <c r="AV168" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW168" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX168" t="n">
         <v>8</v>
       </c>
       <c r="AY168" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ168" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA168" t="n">
         <v>3</v>
@@ -37311,43 +37311,43 @@
         <v>1.7</v>
       </c>
       <c r="AN169" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="AO169" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AP169" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AR169" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AS169" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AT169" t="n">
-        <v>2.46</v>
+        <v>2.24</v>
       </c>
       <c r="AU169" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV169" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW169" t="n">
         <v>7</v>
       </c>
-      <c r="AV169" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW169" t="n">
-        <v>5</v>
-      </c>
       <c r="AX169" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY169" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AZ169" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA169" t="n">
         <v>5</v>
@@ -37529,25 +37529,25 @@
         <v>1.11</v>
       </c>
       <c r="AN170" t="n">
-        <v>1.22</v>
+        <v>1.56</v>
       </c>
       <c r="AO170" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AP170" t="n">
-        <v>0.96</v>
+        <v>1.25</v>
       </c>
       <c r="AQ170" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AR170" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AS170" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AT170" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AU170" t="n">
         <v>1</v>
@@ -37556,16 +37556,16 @@
         <v>2</v>
       </c>
       <c r="AW170" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX170" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY170" t="n">
         <v>5</v>
       </c>
-      <c r="AX170" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY170" t="n">
-        <v>6</v>
-      </c>
       <c r="AZ170" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BA170" t="n">
         <v>5</v>
@@ -37747,28 +37747,28 @@
         <v>1.42</v>
       </c>
       <c r="AN171" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="AO171" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AQ171" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR171" t="n">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="AS171" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AT171" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AU171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV171" t="n">
         <v>2</v>
@@ -37780,7 +37780,7 @@
         <v>4</v>
       </c>
       <c r="AY171" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ171" t="n">
         <v>6</v>
@@ -37965,31 +37965,31 @@
         <v>0</v>
       </c>
       <c r="AN172" t="n">
-        <v>1.17</v>
+        <v>0.8</v>
       </c>
       <c r="AO172" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AP172" t="n">
-        <v>1.16</v>
+        <v>0.79</v>
       </c>
       <c r="AQ172" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AR172" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AS172" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="AT172" t="n">
-        <v>2.11</v>
+        <v>2.22</v>
       </c>
       <c r="AU172" t="n">
         <v>4</v>
       </c>
       <c r="AV172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW172" t="n">
         <v>12</v>
@@ -38001,7 +38001,7 @@
         <v>16</v>
       </c>
       <c r="AZ172" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA172" t="n">
         <v>7</v>
@@ -38183,40 +38183,40 @@
         <v>1.36</v>
       </c>
       <c r="AN173" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AO173" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AP173" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ173" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AR173" t="n">
         <v>0.84</v>
       </c>
-      <c r="AO173" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AP173" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="AQ173" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AR173" t="n">
-        <v>0.86</v>
-      </c>
       <c r="AS173" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AT173" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="AU173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV173" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW173" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX173" t="n">
         <v>4</v>
       </c>
-      <c r="AW173" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX173" t="n">
-        <v>3</v>
-      </c>
       <c r="AY173" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AZ173" t="n">
         <v>7</v>
@@ -38401,43 +38401,43 @@
         <v>1.52</v>
       </c>
       <c r="AN174" t="n">
-        <v>0.83</v>
+        <v>1.22</v>
       </c>
       <c r="AO174" t="n">
-        <v>1.05</v>
+        <v>0.88</v>
       </c>
       <c r="AP174" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AQ174" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AR174" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AS174" t="n">
         <v>0.92</v>
       </c>
-      <c r="AR174" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="AS174" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AT174" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AU174" t="n">
         <v>1</v>
       </c>
       <c r="AV174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW174" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX174" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY174" t="n">
         <v>6</v>
       </c>
-      <c r="AX174" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY174" t="n">
+      <c r="AZ174" t="n">
         <v>7</v>
-      </c>
-      <c r="AZ174" t="n">
-        <v>4</v>
       </c>
       <c r="BA174" t="n">
         <v>0</v>
@@ -38619,43 +38619,43 @@
         <v>1.03</v>
       </c>
       <c r="AN175" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="AO175" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="AP175" t="n">
-        <v>0.96</v>
+        <v>1.25</v>
       </c>
       <c r="AQ175" t="n">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="AR175" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AS175" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AT175" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AU175" t="n">
         <v>2</v>
       </c>
       <c r="AV175" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW175" t="n">
         <v>4</v>
       </c>
       <c r="AX175" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY175" t="n">
         <v>6</v>
       </c>
       <c r="AZ175" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA175" t="n">
         <v>4</v>
@@ -38759,7 +38759,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>['45', '45+5']</t>
+          <t>['45+5', '45']</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
@@ -38837,43 +38837,43 @@
         <v>1.1</v>
       </c>
       <c r="AN176" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AO176" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AP176" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ176" t="n">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="AR176" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AS176" t="n">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="AT176" t="n">
-        <v>2.97</v>
+        <v>2.85</v>
       </c>
       <c r="AU176" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV176" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AW176" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AX176" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AY176" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AZ176" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="BA176" t="n">
         <v>4</v>
@@ -39058,22 +39058,22 @@
         <v>1.5</v>
       </c>
       <c r="AO177" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AP177" t="n">
-        <v>1.48</v>
+        <v>1.23</v>
       </c>
       <c r="AQ177" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AR177" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AS177" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AT177" t="n">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="AU177" t="n">
         <v>4</v>
@@ -39082,16 +39082,16 @@
         <v>8</v>
       </c>
       <c r="AW177" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX177" t="n">
         <v>5</v>
       </c>
-      <c r="AX177" t="n">
-        <v>4</v>
-      </c>
       <c r="AY177" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ177" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA177" t="n">
         <v>6</v>
@@ -39273,40 +39273,40 @@
         <v>1.2</v>
       </c>
       <c r="AN178" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AO178" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AP178" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AQ178" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AR178" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AS178" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AT178" t="n">
-        <v>2.49</v>
+        <v>2.32</v>
       </c>
       <c r="AU178" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV178" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW178" t="n">
         <v>4</v>
       </c>
       <c r="AX178" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY178" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ178" t="n">
         <v>15</v>
@@ -39491,28 +39491,28 @@
         <v>1.45</v>
       </c>
       <c r="AN179" t="n">
-        <v>1.05</v>
+        <v>0.88</v>
       </c>
       <c r="AO179" t="n">
         <v>0.8</v>
       </c>
       <c r="AP179" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AQ179" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="AR179" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AS179" t="n">
-        <v>0.85</v>
+        <v>0.91</v>
       </c>
       <c r="AT179" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="AU179" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV179" t="n">
         <v>1</v>
@@ -39524,7 +39524,7 @@
         <v>6</v>
       </c>
       <c r="AY179" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ179" t="n">
         <v>7</v>
@@ -39709,40 +39709,40 @@
         <v>1.32</v>
       </c>
       <c r="AN180" t="n">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="AO180" t="n">
-        <v>1.11</v>
+        <v>1.63</v>
       </c>
       <c r="AP180" t="n">
-        <v>1.28</v>
+        <v>1.07</v>
       </c>
       <c r="AQ180" t="n">
-        <v>1.16</v>
+        <v>1.64</v>
       </c>
       <c r="AR180" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AS180" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT180" t="n">
-        <v>2.37</v>
+        <v>2.21</v>
       </c>
       <c r="AU180" t="n">
         <v>2</v>
       </c>
       <c r="AV180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW180" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX180" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY180" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ180" t="n">
         <v>6</v>
@@ -39927,43 +39927,43 @@
         <v>1.68</v>
       </c>
       <c r="AN181" t="n">
-        <v>0.95</v>
+        <v>1.4</v>
       </c>
       <c r="AO181" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AP181" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AQ181" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AR181" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AS181" t="n">
-        <v>1.04</v>
+        <v>0.97</v>
       </c>
       <c r="AT181" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AU181" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV181" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW181" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AX181" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AY181" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AZ181" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="BA181" t="n">
         <v>6</v>
@@ -40145,40 +40145,40 @@
         <v>1.61</v>
       </c>
       <c r="AN182" t="n">
-        <v>0.68</v>
+        <v>0.9</v>
       </c>
       <c r="AO182" t="n">
-        <v>1</v>
+        <v>0.78</v>
       </c>
       <c r="AP182" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AQ182" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AR182" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AS182" t="n">
         <v>0.92</v>
       </c>
-      <c r="AR182" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="AS182" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AT182" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AU182" t="n">
         <v>4</v>
       </c>
       <c r="AV182" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW182" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX182" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AY182" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ182" t="n">
         <v>12</v>
@@ -40363,43 +40363,43 @@
         <v>1.04</v>
       </c>
       <c r="AN183" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AO183" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AP183" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AQ183" t="n">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="AR183" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AS183" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AT183" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AU183" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV183" t="n">
         <v>5</v>
       </c>
-      <c r="AV183" t="n">
-        <v>6</v>
-      </c>
       <c r="AW183" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX183" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AY183" t="n">
         <v>9</v>
       </c>
       <c r="AZ183" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA183" t="n">
         <v>5</v>
@@ -40581,43 +40581,43 @@
         <v>4.4</v>
       </c>
       <c r="AN184" t="n">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="AO184" t="n">
-        <v>1.1</v>
+        <v>0.89</v>
       </c>
       <c r="AP184" t="n">
-        <v>2.32</v>
+        <v>2.54</v>
       </c>
       <c r="AQ184" t="n">
-        <v>0.96</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR184" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AS184" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="AT184" t="n">
-        <v>2.54</v>
+        <v>2.69</v>
       </c>
       <c r="AU184" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AV184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW184" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AX184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY184" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AZ184" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BA184" t="n">
         <v>10</v>
@@ -40799,25 +40799,25 @@
         <v>1.33</v>
       </c>
       <c r="AN185" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AO185" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AP185" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ185" t="n">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="AR185" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AS185" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AT185" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="AU185" t="n">
         <v>0</v>
@@ -40826,16 +40826,16 @@
         <v>5</v>
       </c>
       <c r="AW185" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX185" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AY185" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AZ185" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="BA185" t="n">
         <v>2</v>
@@ -41017,28 +41017,28 @@
         <v>1.25</v>
       </c>
       <c r="AN186" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AO186" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AP186" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AQ186" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AR186" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AS186" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="AT186" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AU186" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV186" t="n">
         <v>4</v>
@@ -41050,7 +41050,7 @@
         <v>5</v>
       </c>
       <c r="AY186" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ186" t="n">
         <v>9</v>
@@ -41235,28 +41235,28 @@
         <v>1.49</v>
       </c>
       <c r="AN187" t="n">
-        <v>1.05</v>
+        <v>0.89</v>
       </c>
       <c r="AO187" t="n">
-        <v>1.1</v>
+        <v>1.56</v>
       </c>
       <c r="AP187" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AQ187" t="n">
-        <v>1.16</v>
+        <v>1.64</v>
       </c>
       <c r="AR187" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AS187" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="AT187" t="n">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="AU187" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV187" t="n">
         <v>1</v>
@@ -41265,13 +41265,13 @@
         <v>7</v>
       </c>
       <c r="AX187" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY187" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ187" t="n">
         <v>7</v>
-      </c>
-      <c r="AY187" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ187" t="n">
-        <v>8</v>
       </c>
       <c r="BA187" t="n">
         <v>1</v>
@@ -41453,22 +41453,22 @@
         <v>1.45</v>
       </c>
       <c r="AN188" t="n">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="AO188" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AP188" t="n">
-        <v>1.28</v>
+        <v>1.07</v>
       </c>
       <c r="AQ188" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AR188" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AS188" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="AT188" t="n">
         <v>2.09</v>
@@ -41480,13 +41480,13 @@
         <v>2</v>
       </c>
       <c r="AW188" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX188" t="n">
         <v>6</v>
       </c>
       <c r="AY188" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ188" t="n">
         <v>8</v>
@@ -41671,25 +41671,25 @@
         <v>1.22</v>
       </c>
       <c r="AN189" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AO189" t="n">
-        <v>0.8</v>
+        <v>0.33</v>
       </c>
       <c r="AP189" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AQ189" t="n">
-        <v>1.08</v>
+        <v>0.85</v>
       </c>
       <c r="AR189" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AS189" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="AT189" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AU189" t="n">
         <v>0</v>
@@ -41698,16 +41698,16 @@
         <v>3</v>
       </c>
       <c r="AW189" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX189" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AY189" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ189" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="BA189" t="n">
         <v>1</v>
@@ -41889,43 +41889,43 @@
         <v>1.32</v>
       </c>
       <c r="AN190" t="n">
-        <v>0.8100000000000001</v>
+        <v>1</v>
       </c>
       <c r="AO190" t="n">
-        <v>0.9</v>
+        <v>0.44</v>
       </c>
       <c r="AP190" t="n">
-        <v>0.84</v>
+        <v>1</v>
       </c>
       <c r="AQ190" t="n">
-        <v>1.08</v>
+        <v>0.92</v>
       </c>
       <c r="AR190" t="n">
         <v>0.85</v>
       </c>
       <c r="AS190" t="n">
-        <v>0.88</v>
+        <v>0.99</v>
       </c>
       <c r="AT190" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AU190" t="n">
         <v>0</v>
       </c>
       <c r="AV190" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AW190" t="n">
         <v>3</v>
       </c>
       <c r="AX190" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AY190" t="n">
         <v>3</v>
       </c>
       <c r="AZ190" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="BA190" t="n">
         <v>5</v>
@@ -42107,43 +42107,43 @@
         <v>2.7</v>
       </c>
       <c r="AN191" t="n">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="AO191" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AP191" t="n">
-        <v>2.32</v>
+        <v>2.54</v>
       </c>
       <c r="AQ191" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AR191" t="n">
-        <v>1.64</v>
+        <v>1.88</v>
       </c>
       <c r="AS191" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AT191" t="n">
-        <v>2.76</v>
+        <v>3.08</v>
       </c>
       <c r="AU191" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV191" t="n">
         <v>5</v>
       </c>
       <c r="AW191" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX191" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY191" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ191" t="n">
         <v>10</v>
-      </c>
-      <c r="AX191" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY191" t="n">
-        <v>19</v>
-      </c>
-      <c r="AZ191" t="n">
-        <v>11</v>
       </c>
       <c r="BA191" t="n">
         <v>6</v>
@@ -42325,25 +42325,25 @@
         <v>1.22</v>
       </c>
       <c r="AN192" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO192" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AP192" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AQ192" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AR192" t="n">
         <v>1.5</v>
       </c>
-      <c r="AO192" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AP192" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AQ192" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AR192" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AS192" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AT192" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AU192" t="n">
         <v>4</v>
@@ -42352,25 +42352,25 @@
         <v>4</v>
       </c>
       <c r="AW192" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX192" t="n">
         <v>2</v>
       </c>
       <c r="AY192" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ192" t="n">
         <v>6</v>
       </c>
       <c r="BA192" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB192" t="n">
         <v>4</v>
       </c>
       <c r="BC192" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD192" t="n">
         <v>2</v>
@@ -42543,43 +42543,43 @@
         <v>1.49</v>
       </c>
       <c r="AN193" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AO193" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AP193" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AQ193" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AR193" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AS193" t="n">
         <v>1.29</v>
       </c>
       <c r="AT193" t="n">
-        <v>2.37</v>
+        <v>2.47</v>
       </c>
       <c r="AU193" t="n">
         <v>3</v>
       </c>
       <c r="AV193" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AW193" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX193" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AY193" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ193" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="BA193" t="n">
         <v>7</v>
@@ -42761,25 +42761,25 @@
         <v>1.15</v>
       </c>
       <c r="AN194" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AO194" t="n">
-        <v>2.24</v>
+        <v>2.09</v>
       </c>
       <c r="AP194" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AQ194" t="n">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="AR194" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AS194" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AT194" t="n">
-        <v>2.61</v>
+        <v>2.52</v>
       </c>
       <c r="AU194" t="n">
         <v>8</v>
@@ -42788,16 +42788,16 @@
         <v>6</v>
       </c>
       <c r="AW194" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX194" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY194" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ194" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA194" t="n">
         <v>1</v>
@@ -42979,25 +42979,25 @@
         <v>0</v>
       </c>
       <c r="AN195" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AO195" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AP195" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AQ195" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AR195" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AS195" t="n">
         <v>0.95</v>
       </c>
-      <c r="AP195" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AQ195" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="AR195" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="AS195" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AT195" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AU195" t="n">
         <v>3</v>
@@ -43006,16 +43006,16 @@
         <v>2</v>
       </c>
       <c r="AW195" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX195" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY195" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ195" t="n">
         <v>8</v>
-      </c>
-      <c r="AZ195" t="n">
-        <v>5</v>
       </c>
       <c r="BA195" t="n">
         <v>7</v>
@@ -43197,40 +43197,40 @@
         <v>1.57</v>
       </c>
       <c r="AN196" t="n">
-        <v>1.05</v>
+        <v>0.9</v>
       </c>
       <c r="AO196" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="AP196" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AQ196" t="n">
-        <v>1.08</v>
+        <v>0.92</v>
       </c>
       <c r="AR196" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AS196" t="n">
-        <v>0.88</v>
+        <v>1.03</v>
       </c>
       <c r="AT196" t="n">
-        <v>2.09</v>
+        <v>2.31</v>
       </c>
       <c r="AU196" t="n">
         <v>4</v>
       </c>
       <c r="AV196" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW196" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX196" t="n">
         <v>3</v>
       </c>
-      <c r="AW196" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX196" t="n">
-        <v>2</v>
-      </c>
       <c r="AY196" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AZ196" t="n">
         <v>5</v>
@@ -43415,25 +43415,25 @@
         <v>1.37</v>
       </c>
       <c r="AN197" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AO197" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="AP197" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AQ197" t="n">
-        <v>1.16</v>
+        <v>1.64</v>
       </c>
       <c r="AR197" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AS197" t="n">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="AT197" t="n">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="AU197" t="n">
         <v>3</v>
@@ -43442,25 +43442,25 @@
         <v>1</v>
       </c>
       <c r="AW197" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX197" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY197" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ197" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA197" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB197" t="n">
         <v>2</v>
       </c>
       <c r="BC197" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD197" t="n">
         <v>2.24</v>
@@ -43633,43 +43633,43 @@
         <v>1.45</v>
       </c>
       <c r="AN198" t="n">
-        <v>1.32</v>
+        <v>1.08</v>
       </c>
       <c r="AO198" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="AP198" t="n">
-        <v>1.28</v>
+        <v>1.07</v>
       </c>
       <c r="AQ198" t="n">
-        <v>1.08</v>
+        <v>0.85</v>
       </c>
       <c r="AR198" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AS198" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AT198" t="n">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="AU198" t="n">
         <v>5</v>
       </c>
       <c r="AV198" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW198" t="n">
         <v>5</v>
       </c>
       <c r="AX198" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY198" t="n">
         <v>10</v>
       </c>
       <c r="AZ198" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BA198" t="n">
         <v>3</v>
@@ -43851,31 +43851,31 @@
         <v>1.22</v>
       </c>
       <c r="AN199" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AO199" t="n">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AP199" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AQ199" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AR199" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="AS199" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AT199" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AU199" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV199" t="n">
         <v>4</v>
-      </c>
-      <c r="AV199" t="n">
-        <v>7</v>
       </c>
       <c r="AW199" t="n">
         <v>7</v>
@@ -43884,10 +43884,10 @@
         <v>9</v>
       </c>
       <c r="AY199" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ199" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA199" t="n">
         <v>2</v>
@@ -44069,43 +44069,43 @@
         <v>1.12</v>
       </c>
       <c r="AN200" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AO200" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="AP200" t="n">
-        <v>1.48</v>
+        <v>1.23</v>
       </c>
       <c r="AQ200" t="n">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="AR200" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AS200" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AT200" t="n">
-        <v>3.08</v>
+        <v>2.99</v>
       </c>
       <c r="AU200" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV200" t="n">
         <v>2</v>
       </c>
       <c r="AW200" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX200" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY200" t="n">
         <v>8</v>
       </c>
       <c r="AZ200" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA200" t="n">
         <v>2</v>
@@ -44287,43 +44287,43 @@
         <v>1.1</v>
       </c>
       <c r="AN201" t="n">
-        <v>1.05</v>
+        <v>1.27</v>
       </c>
       <c r="AO201" t="n">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="AP201" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ201" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR201" t="n">
         <v>0.96</v>
       </c>
-      <c r="AQ201" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR201" t="n">
-        <v>0.88</v>
-      </c>
       <c r="AS201" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AT201" t="n">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="AU201" t="n">
         <v>2</v>
       </c>
       <c r="AV201" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW201" t="n">
         <v>3</v>
       </c>
       <c r="AX201" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AY201" t="n">
         <v>5</v>
       </c>
       <c r="AZ201" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA201" t="n">
         <v>3</v>
@@ -44505,43 +44505,43 @@
         <v>1.33</v>
       </c>
       <c r="AN202" t="n">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="AO202" t="n">
-        <v>2.14</v>
+        <v>1.92</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ202" t="n">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="AR202" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="AS202" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AT202" t="n">
-        <v>2.79</v>
+        <v>2.9</v>
       </c>
       <c r="AU202" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV202" t="n">
         <v>3</v>
       </c>
       <c r="AW202" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX202" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY202" t="n">
         <v>10</v>
       </c>
       <c r="AZ202" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA202" t="n">
         <v>2</v>
@@ -44723,40 +44723,40 @@
         <v>1.27</v>
       </c>
       <c r="AN203" t="n">
-        <v>0.77</v>
+        <v>0.91</v>
       </c>
       <c r="AO203" t="n">
-        <v>0.91</v>
+        <v>0.64</v>
       </c>
       <c r="AP203" t="n">
-        <v>0.84</v>
+        <v>1</v>
       </c>
       <c r="AQ203" t="n">
-        <v>1.08</v>
+        <v>0.85</v>
       </c>
       <c r="AR203" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="AS203" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AT203" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AU203" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV203" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW203" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AX203" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY203" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ203" t="n">
         <v>12</v>
@@ -44941,40 +44941,40 @@
         <v>1.23</v>
       </c>
       <c r="AN204" t="n">
-        <v>1.18</v>
+        <v>0.73</v>
       </c>
       <c r="AO204" t="n">
-        <v>1.09</v>
+        <v>0.91</v>
       </c>
       <c r="AP204" t="n">
-        <v>1.16</v>
+        <v>0.79</v>
       </c>
       <c r="AQ204" t="n">
-        <v>1.08</v>
+        <v>0.92</v>
       </c>
       <c r="AR204" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AS204" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AT204" t="n">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="AU204" t="n">
         <v>1</v>
       </c>
       <c r="AV204" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW204" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX204" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY204" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AZ204" t="n">
         <v>4</v>
@@ -45159,25 +45159,25 @@
         <v>1.69</v>
       </c>
       <c r="AN205" t="n">
-        <v>0.95</v>
+        <v>1.18</v>
       </c>
       <c r="AO205" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AP205" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ205" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AR205" t="n">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="AS205" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT205" t="n">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="AU205" t="n">
         <v>7</v>
@@ -45377,43 +45377,43 @@
         <v>1.4</v>
       </c>
       <c r="AN206" t="n">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="AO206" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AP206" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AQ206" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AR206" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AS206" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="AT206" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AU206" t="n">
         <v>2</v>
       </c>
       <c r="AV206" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW206" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX206" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY206" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ206" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA206" t="n">
         <v>4</v>
@@ -45595,43 +45595,43 @@
         <v>1.64</v>
       </c>
       <c r="AN207" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AO207" t="n">
         <v>1.64</v>
       </c>
-      <c r="AO207" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AP207" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AQ207" t="n">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="AR207" t="n">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="AS207" t="n">
         <v>1.4</v>
       </c>
       <c r="AT207" t="n">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="AU207" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV207" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AW207" t="n">
         <v>7</v>
       </c>
       <c r="AX207" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY207" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ207" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA207" t="n">
         <v>4</v>
@@ -45813,25 +45813,25 @@
         <v>2.5</v>
       </c>
       <c r="AN208" t="n">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="AO208" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AP208" t="n">
-        <v>2.32</v>
+        <v>2.54</v>
       </c>
       <c r="AQ208" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AR208" t="n">
-        <v>1.64</v>
+        <v>1.87</v>
       </c>
       <c r="AS208" t="n">
         <v>1.17</v>
       </c>
       <c r="AT208" t="n">
-        <v>2.81</v>
+        <v>3.04</v>
       </c>
       <c r="AU208" t="n">
         <v>4</v>
@@ -45840,13 +45840,13 @@
         <v>1</v>
       </c>
       <c r="AW208" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX208" t="n">
         <v>2</v>
       </c>
       <c r="AY208" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ208" t="n">
         <v>3</v>
@@ -46034,40 +46034,40 @@
         <v>1.18</v>
       </c>
       <c r="AO209" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AP209" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ209" t="n">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="AR209" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AS209" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AT209" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="AU209" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV209" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW209" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX209" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY209" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ209" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BA209" t="n">
         <v>4</v>
@@ -46249,43 +46249,43 @@
         <v>1.65</v>
       </c>
       <c r="AN210" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AO210" t="n">
-        <v>1.05</v>
+        <v>0.8</v>
       </c>
       <c r="AP210" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AQ210" t="n">
-        <v>0.96</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR210" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="AS210" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AT210" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="AU210" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW210" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AX210" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY210" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AZ210" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA210" t="n">
         <v>6</v>
@@ -46467,34 +46467,34 @@
         <v>1.16</v>
       </c>
       <c r="AN211" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AO211" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AP211" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ211" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AR211" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AS211" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AT211" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="AU211" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AV211" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW211" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AX211" t="n">
         <v>4</v>
@@ -46503,7 +46503,7 @@
         <v>17</v>
       </c>
       <c r="AZ211" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA211" t="n">
         <v>4</v>
@@ -46685,43 +46685,43 @@
         <v>2.83</v>
       </c>
       <c r="AN212" t="n">
-        <v>1.48</v>
+        <v>1.18</v>
       </c>
       <c r="AO212" t="n">
-        <v>1.04</v>
+        <v>0.82</v>
       </c>
       <c r="AP212" t="n">
-        <v>1.48</v>
+        <v>1.23</v>
       </c>
       <c r="AQ212" t="n">
-        <v>0.96</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR212" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AS212" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AT212" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="AU212" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV212" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW212" t="n">
         <v>4</v>
       </c>
-      <c r="AV212" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW212" t="n">
-        <v>3</v>
-      </c>
       <c r="AX212" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY212" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ212" t="n">
         <v>7</v>
-      </c>
-      <c r="AZ212" t="n">
-        <v>6</v>
       </c>
       <c r="BA212" t="n">
         <v>6</v>
@@ -46903,25 +46903,25 @@
         <v>1.5</v>
       </c>
       <c r="AN213" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AO213" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="AP213" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AQ213" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AR213" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AS213" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AT213" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AU213" t="n">
         <v>0</v>
@@ -47121,25 +47121,25 @@
         <v>1.33</v>
       </c>
       <c r="AN214" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AO214" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AP214" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AQ214" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AR214" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AS214" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="AT214" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AU214" t="n">
         <v>3</v>
@@ -47148,16 +47148,16 @@
         <v>1</v>
       </c>
       <c r="AW214" t="n">
-        <v>7</v>
+        <v>-2</v>
       </c>
       <c r="AX214" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AY214" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AZ214" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA214" t="n">
         <v>5</v>
@@ -47266,7 +47266,7 @@
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>['40']</t>
+          <t>['42']</t>
         </is>
       </c>
       <c r="Q215" t="n">
@@ -47339,43 +47339,43 @@
         <v>1.48</v>
       </c>
       <c r="AN215" t="n">
-        <v>1.09</v>
+        <v>1.27</v>
       </c>
       <c r="AO215" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AP215" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AQ215" t="n">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="AR215" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="AS215" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AT215" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="AU215" t="n">
         <v>1</v>
       </c>
       <c r="AV215" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW215" t="n">
         <v>7</v>
       </c>
       <c r="AX215" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AY215" t="n">
         <v>8</v>
       </c>
       <c r="AZ215" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="BA215" t="n">
         <v>1</v>
@@ -47557,25 +47557,25 @@
         <v>1.45</v>
       </c>
       <c r="AN216" t="n">
-        <v>0.74</v>
+        <v>0.83</v>
       </c>
       <c r="AO216" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AP216" t="n">
-        <v>0.84</v>
+        <v>1</v>
       </c>
       <c r="AQ216" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AR216" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AS216" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AT216" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AU216" t="n">
         <v>4</v>
@@ -47775,52 +47775,52 @@
         <v>1.49</v>
       </c>
       <c r="AN217" t="n">
-        <v>1.17</v>
+        <v>0.75</v>
       </c>
       <c r="AO217" t="n">
-        <v>0.91</v>
+        <v>0.73</v>
       </c>
       <c r="AP217" t="n">
-        <v>1.16</v>
+        <v>0.79</v>
       </c>
       <c r="AQ217" t="n">
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
       <c r="AR217" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AS217" t="n">
-        <v>1.11</v>
+        <v>0.95</v>
       </c>
       <c r="AT217" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AU217" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV217" t="n">
         <v>3</v>
       </c>
       <c r="AW217" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX217" t="n">
         <v>6</v>
       </c>
       <c r="AY217" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AZ217" t="n">
         <v>9</v>
       </c>
       <c r="BA217" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB217" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC217" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BD217" t="n">
         <v>1.86</v>
@@ -47993,43 +47993,43 @@
         <v>2.43</v>
       </c>
       <c r="AN218" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AO218" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AP218" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AQ218" t="n">
-        <v>0.96</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR218" t="n">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="AS218" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AT218" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AU218" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV218" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW218" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX218" t="n">
         <v>6</v>
       </c>
-      <c r="AV218" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW218" t="n">
+      <c r="AY218" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ218" t="n">
         <v>8</v>
-      </c>
-      <c r="AX218" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY218" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ218" t="n">
-        <v>7</v>
       </c>
       <c r="BA218" t="n">
         <v>6</v>
@@ -48211,25 +48211,25 @@
         <v>1.35</v>
       </c>
       <c r="AN219" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AO219" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AP219" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ219" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AR219" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AS219" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AT219" t="n">
-        <v>2.47</v>
+        <v>2.52</v>
       </c>
       <c r="AU219" t="n">
         <v>1</v>
@@ -48238,16 +48238,16 @@
         <v>1</v>
       </c>
       <c r="AW219" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AX219" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AY219" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AZ219" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BA219" t="n">
         <v>4</v>
@@ -48429,43 +48429,43 @@
         <v>1.17</v>
       </c>
       <c r="AN220" t="n">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="AO220" t="n">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="AP220" t="n">
-        <v>1.48</v>
+        <v>1.23</v>
       </c>
       <c r="AQ220" t="n">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="AR220" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AS220" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AT220" t="n">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="AU220" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV220" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW220" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX220" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY220" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ220" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA220" t="n">
         <v>3</v>
@@ -48647,43 +48647,43 @@
         <v>4.33</v>
       </c>
       <c r="AN221" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="AO221" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AP221" t="n">
-        <v>2.32</v>
+        <v>2.54</v>
       </c>
       <c r="AQ221" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AR221" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AS221" t="n">
-        <v>1.12</v>
+        <v>0.9</v>
       </c>
       <c r="AT221" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="AU221" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV221" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW221" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AX221" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY221" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ221" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BA221" t="n">
         <v>9</v>
@@ -48865,43 +48865,43 @@
         <v>1.57</v>
       </c>
       <c r="AN222" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AO222" t="n">
-        <v>1.08</v>
+        <v>0.92</v>
       </c>
       <c r="AP222" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AQ222" t="n">
-        <v>1.08</v>
+        <v>0.92</v>
       </c>
       <c r="AR222" t="n">
-        <v>0.91</v>
+        <v>1.03</v>
       </c>
       <c r="AS222" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="AT222" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AU222" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV222" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW222" t="n">
         <v>4</v>
-      </c>
-      <c r="AW222" t="n">
-        <v>0</v>
       </c>
       <c r="AX222" t="n">
         <v>4</v>
       </c>
       <c r="AY222" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AZ222" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA222" t="n">
         <v>1</v>
@@ -49083,43 +49083,43 @@
         <v>1.32</v>
       </c>
       <c r="AN223" t="n">
-        <v>1.17</v>
+        <v>0.77</v>
       </c>
       <c r="AO223" t="n">
-        <v>1.08</v>
+        <v>0.83</v>
       </c>
       <c r="AP223" t="n">
-        <v>1.16</v>
+        <v>0.79</v>
       </c>
       <c r="AQ223" t="n">
-        <v>1.08</v>
+        <v>0.85</v>
       </c>
       <c r="AR223" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AS223" t="n">
         <v>1.14</v>
       </c>
-      <c r="AS223" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AT223" t="n">
-        <v>2.2</v>
+        <v>2.49</v>
       </c>
       <c r="AU223" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AV223" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW223" t="n">
         <v>4</v>
       </c>
       <c r="AX223" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AY223" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ223" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BA223" t="n">
         <v>0</v>
@@ -49301,43 +49301,43 @@
         <v>1.42</v>
       </c>
       <c r="AN224" t="n">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="AO224" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AP224" t="n">
-        <v>1.28</v>
+        <v>1.07</v>
       </c>
       <c r="AQ224" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR224" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AS224" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AT224" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AU224" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV224" t="n">
         <v>0</v>
       </c>
       <c r="AW224" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX224" t="n">
         <v>6</v>
       </c>
-      <c r="AX224" t="n">
-        <v>5</v>
-      </c>
       <c r="AY224" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ224" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA224" t="n">
         <v>1</v>
@@ -49519,40 +49519,40 @@
         <v>1.86</v>
       </c>
       <c r="AN225" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AO225" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AP225" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AQ225" t="n">
         <v>0.83</v>
       </c>
-      <c r="AP225" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="AQ225" t="n">
-        <v>0.84</v>
-      </c>
       <c r="AR225" t="n">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="AS225" t="n">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="AT225" t="n">
-        <v>1.99</v>
+        <v>2.18</v>
       </c>
       <c r="AU225" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AV225" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW225" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX225" t="n">
         <v>3</v>
       </c>
-      <c r="AW225" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX225" t="n">
-        <v>2</v>
-      </c>
       <c r="AY225" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AZ225" t="n">
         <v>5</v>
@@ -49737,25 +49737,25 @@
         <v>2.16</v>
       </c>
       <c r="AN226" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AO226" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AP226" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ226" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AR226" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AS226" t="n">
-        <v>1.11</v>
+        <v>0.93</v>
       </c>
       <c r="AT226" t="n">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="AU226" t="n">
         <v>2</v>
